--- a/artfynd/A 35466-2026 artfynd.xlsx
+++ b/artfynd/A 35466-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373315</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35466-2026 artfynd.xlsx
+++ b/artfynd/A 35466-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373315</v>
       </c>
       <c r="B2" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373314</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35466-2026 artfynd.xlsx
+++ b/artfynd/A 35466-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373315</v>
       </c>
       <c r="B2" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35466-2026 artfynd.xlsx
+++ b/artfynd/A 35466-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373315</v>
       </c>
       <c r="B2" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35466-2026 artfynd.xlsx
+++ b/artfynd/A 35466-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373315</v>
       </c>
       <c r="B2" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35466-2026 artfynd.xlsx
+++ b/artfynd/A 35466-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373315</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373314</v>
       </c>
       <c r="B3" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
